--- a/Data/Lantern.xlsx
+++ b/Data/Lantern.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{134873E6-F95B-46A9-BB48-F9ECF54ED627}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201E677F-EA23-4D47-9FD1-1B0E0E7C2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="1755" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="42195" yWindow="210" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lantern" sheetId="1" r:id="rId1"/>
@@ -387,7 +387,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -399,9 +399,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -722,7 +719,7 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
     </row>
@@ -737,7 +734,7 @@
         <v>7</v>
       </c>
       <c r="D2" s="2">
-        <v>3001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -751,7 +748,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="3">
-        <v>3002</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -765,7 +762,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="3">
-        <v>3003</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -779,7 +776,7 @@
         <v>10</v>
       </c>
       <c r="D5" s="3">
-        <v>3004</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -793,7 +790,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="4">
-        <v>3001</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -807,7 +804,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="4">
-        <v>3002</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -821,7 +818,7 @@
         <v>15</v>
       </c>
       <c r="D8" s="4">
-        <v>3003</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -835,7 +832,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="4">
-        <v>3004</v>
+        <v>5008</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -849,7 +846,7 @@
         <v>18</v>
       </c>
       <c r="D10" s="5">
-        <v>3001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -863,7 +860,7 @@
         <v>20</v>
       </c>
       <c r="D11" s="5">
-        <v>3002</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -877,7 +874,7 @@
         <v>22</v>
       </c>
       <c r="D12" s="5">
-        <v>3003</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -891,7 +888,7 @@
         <v>24</v>
       </c>
       <c r="D13" s="5">
-        <v>3004</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -905,7 +902,7 @@
         <v>26</v>
       </c>
       <c r="D14" s="6">
-        <v>3001</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -919,7 +916,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="6">
-        <v>3002</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -933,7 +930,7 @@
         <v>30</v>
       </c>
       <c r="D16" s="6">
-        <v>3003</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -947,7 +944,7 @@
         <v>32</v>
       </c>
       <c r="D17" s="6">
-        <v>3004</v>
+        <v>5008</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -961,7 +958,7 @@
         <v>34</v>
       </c>
       <c r="D18" s="3">
-        <v>3001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -975,7 +972,7 @@
         <v>36</v>
       </c>
       <c r="D19" s="3">
-        <v>3002</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -989,7 +986,7 @@
         <v>38</v>
       </c>
       <c r="D20" s="3">
-        <v>3003</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1003,7 +1000,7 @@
         <v>40</v>
       </c>
       <c r="D21" s="3">
-        <v>3004</v>
+        <v>5004</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1017,7 +1014,7 @@
         <v>42</v>
       </c>
       <c r="D22" s="4">
-        <v>3001</v>
+        <v>5005</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1031,7 +1028,7 @@
         <v>44</v>
       </c>
       <c r="D23" s="4">
-        <v>3002</v>
+        <v>5006</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1045,7 +1042,7 @@
         <v>46</v>
       </c>
       <c r="D24" s="4">
-        <v>3003</v>
+        <v>5007</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1059,7 +1056,7 @@
         <v>48</v>
       </c>
       <c r="D25" s="4">
-        <v>3004</v>
+        <v>5008</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1073,7 +1070,7 @@
         <v>50</v>
       </c>
       <c r="D26" s="5">
-        <v>3001</v>
+        <v>5001</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1087,7 +1084,7 @@
         <v>52</v>
       </c>
       <c r="D27" s="5">
-        <v>3002</v>
+        <v>5002</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1101,7 +1098,7 @@
         <v>54</v>
       </c>
       <c r="D28" s="5">
-        <v>3003</v>
+        <v>5003</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1115,7 +1112,7 @@
         <v>56</v>
       </c>
       <c r="D29" s="8">
-        <v>3004</v>
+        <v>5004</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Lantern.xlsx
+++ b/Data/Lantern.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{201E677F-EA23-4D47-9FD1-1B0E0E7C2085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA47732-437D-4617-BED1-3F90BC032B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42195" yWindow="210" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="47445" yWindow="1830" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lantern" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="59">
   <si>
     <t>ItemId</t>
   </si>
@@ -42,216 +42,221 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>Attack_Inc=0.18</t>
+  </si>
+  <si>
+    <t>Attack_Inc=0.21</t>
+  </si>
+  <si>
+    <t>Attack_Inc=0.25</t>
+  </si>
+  <si>
+    <t>OwnStat</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=0.043</t>
+  </si>
+  <si>
+    <t>Attack_Inc=0.051</t>
+  </si>
+  <si>
+    <t>Attack_Inc=0.06</t>
+  </si>
+  <si>
+    <t>Attack_Inc=0.071</t>
+  </si>
+  <si>
+    <t>Attack_Inc=0.313</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=0.391</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=0.489</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=0.611</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=0.764</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=4|AttackSpeed_Inc=0.02</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=0.955</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=5|AttackSpeed_Inc=0.02</t>
+  </si>
+  <si>
+    <t>Attack_Inc=1.194</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=6|AttackSpeed_Inc=0.02</t>
+  </si>
+  <si>
+    <t>Attack_Inc=1.493</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=7|AttackSpeed_Inc=0.02</t>
+  </si>
+  <si>
+    <t>Attack_Inc=1.941</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=9|AttackSpeed_Inc=0.03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=2.523</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=11|AttackSpeed_Inc=0.03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=3.28</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=13|AttackSpeed_Inc=0.03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=4.264</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=15|AttackSpeed_Inc=0.03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=5.543</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=17|AttackSpeed_Inc=0.04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=7.206</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=19|AttackSpeed_Inc=0.04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=9.368</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=21|AttackSpeed_Inc=0.04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=12.178</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=23|AttackSpeed_Inc=0.04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=16.197</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=25|AttackSpeed_Inc=0.06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=21.542</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=27|AttackSpeed_Inc=0.06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=28.651</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=30|AttackSpeed_Inc=0.06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=38.106</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=33|AttackSpeed_Inc=0.06</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=51.443</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=40|AttackSpeed_Inc=0.08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=69.448</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=45|AttackSpeed_Inc=0.08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=93.755</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=50|AttackSpeed_Inc=0.08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack_Inc=126.569</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=55|AttackSpeed_Inc=0.08</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Skill</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpineResourceId</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Attack_Inc=0.15</t>
-  </si>
-  <si>
-    <t>Attack_Inc=0.18</t>
-  </si>
-  <si>
-    <t>Attack_Inc=0.21</t>
-  </si>
-  <si>
-    <t>Attack_Inc=0.25</t>
-  </si>
-  <si>
-    <t>OwnStat</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=0.043</t>
-  </si>
-  <si>
-    <t>Attack_Inc=0.051</t>
-  </si>
-  <si>
-    <t>Attack_Inc=0.06</t>
-  </si>
-  <si>
-    <t>Attack_Inc=0.071</t>
-  </si>
-  <si>
-    <t>Attack_Inc=0.313</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=0.391</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=0.489</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=0.611</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=0.764</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=4|AttackSpeed_Inc=0.02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=0.955</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=5|AttackSpeed_Inc=0.02</t>
-  </si>
-  <si>
-    <t>Attack_Inc=1.194</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=6|AttackSpeed_Inc=0.02</t>
-  </si>
-  <si>
-    <t>Attack_Inc=1.493</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=7|AttackSpeed_Inc=0.02</t>
-  </si>
-  <si>
-    <t>Attack_Inc=1.941</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=9|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=2.523</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=11|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=3.28</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=13|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=4.264</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=15|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=5.543</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=17|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=7.206</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=19|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=9.368</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=21|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=12.178</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=23|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=16.197</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=25|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=21.542</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=27|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=28.651</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=30|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=38.106</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=33|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=51.443</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=40|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=69.448</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=45|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=93.755</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=50|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Attack_Inc=126.569</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Accuracy=55|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Skill</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -701,417 +706,505 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.5" customWidth="1"/>
+    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="D1" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>8101</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
+      <c r="B2" s="2">
+        <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="2">
+        <v>58</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2">
         <v>5001</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>8102</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
+      <c r="B3" s="3">
+        <v>98</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="3">
         <v>5002</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>8103</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
+      <c r="B4" s="3">
+        <v>99</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="3">
         <v>5003</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>8104</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
+      <c r="B5" s="3">
+        <v>100</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="3">
         <v>5004</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>8201</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="4">
+        <v>97</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="4">
+      <c r="E6" s="4">
         <v>5005</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>8202</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>13</v>
+      <c r="B7" s="4">
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="4">
         <v>5006</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>8203</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="4">
+        <v>99</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="4">
+      <c r="E8" s="4">
         <v>5007</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8204</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>16</v>
+      <c r="B9" s="4">
+        <v>100</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="4">
         <v>5008</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8301</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="5">
+        <v>97</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="E10" s="5">
         <v>5001</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>8302</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="5">
+        <v>98</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="E11" s="5">
         <v>5002</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>8303</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="5">
+        <v>99</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="E12" s="5">
         <v>5003</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>8304</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="5">
+        <v>100</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="E13" s="5">
         <v>5004</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>8401</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="6">
+        <v>97</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="6">
+      <c r="E14" s="6">
         <v>5005</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>8402</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="6">
+        <v>98</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="6">
+      <c r="E15" s="6">
         <v>5006</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>8403</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="6">
+        <v>99</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="E16" s="6">
         <v>5007</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>8404</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="6">
+        <v>100</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="6">
+      <c r="E17" s="6">
         <v>5008</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="7">
         <v>8501</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="7">
+        <v>97</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="3">
+      <c r="E18" s="3">
         <v>5001</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
         <v>8502</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="7">
+        <v>98</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D19" s="3">
+      <c r="E19" s="3">
         <v>5002</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
         <v>8503</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="7">
+        <v>99</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="E20" s="3">
         <v>5003</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
         <v>8504</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="7">
+        <v>100</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D21" s="3">
+      <c r="E21" s="3">
         <v>5004</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>8601</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="4">
+        <v>97</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="4">
+      <c r="E22" s="4">
         <v>5005</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>8602</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="4">
+        <v>98</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="4">
+      <c r="E23" s="4">
         <v>5006</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>8603</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="4">
+        <v>99</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" s="4">
+      <c r="E24" s="4">
         <v>5007</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>8604</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="4">
+        <v>100</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D25" s="4">
+      <c r="E25" s="4">
         <v>5008</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>8701</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="5">
+        <v>97</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C26" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="E26" s="5">
         <v>5001</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>8702</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="5">
+        <v>98</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="E27" s="5">
         <v>5002</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>8703</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="5">
+        <v>99</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="E28" s="5">
         <v>5003</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
         <v>8704</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="8">
+        <v>100</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="8">
+      <c r="E29" s="8">
         <v>5004</v>
       </c>
     </row>

--- a/Data/Lantern.xlsx
+++ b/Data/Lantern.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AA47732-437D-4617-BED1-3F90BC032B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F051CE-A42C-4642-9F2D-D53A5C71A225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="47445" yWindow="1830" windowWidth="30045" windowHeight="16455" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lantern" sheetId="1" r:id="rId1"/>
@@ -95,159 +95,82 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=4|AttackSpeed_Inc=0.02</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=0.955</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=5|AttackSpeed_Inc=0.02</t>
-  </si>
-  <si>
     <t>Attack_Inc=1.194</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=6|AttackSpeed_Inc=0.02</t>
-  </si>
-  <si>
     <t>Attack_Inc=1.493</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=7|AttackSpeed_Inc=0.02</t>
-  </si>
-  <si>
     <t>Attack_Inc=1.941</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=9|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=2.523</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=11|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=3.28</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=13|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=4.264</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=15|AttackSpeed_Inc=0.03</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=5.543</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=17|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=7.206</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=19|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=9.368</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=21|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=12.178</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=23|AttackSpeed_Inc=0.04</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=16.197</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=25|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=21.542</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=27|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=28.651</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=30|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=38.106</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=33|AttackSpeed_Inc=0.06</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=51.443</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=40|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=69.448</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=45|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=93.755</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=50|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Attack_Inc=126.569</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Accuracy=55|AttackSpeed_Inc=0.08</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Skill</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -258,6 +181,66 @@
   <si>
     <t>Attack_Inc=0.15</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy=4;AttackSpeed_Inc=0.02</t>
+  </si>
+  <si>
+    <t>Accuracy=5;AttackSpeed_Inc=0.02</t>
+  </si>
+  <si>
+    <t>Accuracy=6;AttackSpeed_Inc=0.02</t>
+  </si>
+  <si>
+    <t>Accuracy=7;AttackSpeed_Inc=0.02</t>
+  </si>
+  <si>
+    <t>Accuracy=9;AttackSpeed_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Accuracy=11;AttackSpeed_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Accuracy=13;AttackSpeed_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Accuracy=15;AttackSpeed_Inc=0.03</t>
+  </si>
+  <si>
+    <t>Accuracy=17;AttackSpeed_Inc=0.04</t>
+  </si>
+  <si>
+    <t>Accuracy=19;AttackSpeed_Inc=0.04</t>
+  </si>
+  <si>
+    <t>Accuracy=21;AttackSpeed_Inc=0.04</t>
+  </si>
+  <si>
+    <t>Accuracy=23;AttackSpeed_Inc=0.04</t>
+  </si>
+  <si>
+    <t>Accuracy=25;AttackSpeed_Inc=0.06</t>
+  </si>
+  <si>
+    <t>Accuracy=27;AttackSpeed_Inc=0.06</t>
+  </si>
+  <si>
+    <t>Accuracy=30;AttackSpeed_Inc=0.06</t>
+  </si>
+  <si>
+    <t>Accuracy=33;AttackSpeed_Inc=0.06</t>
+  </si>
+  <si>
+    <t>Accuracy=40;AttackSpeed_Inc=0.08</t>
+  </si>
+  <si>
+    <t>Accuracy=45;AttackSpeed_Inc=0.08</t>
+  </si>
+  <si>
+    <t>Accuracy=50;AttackSpeed_Inc=0.08</t>
+  </si>
+  <si>
+    <t>Accuracy=55;AttackSpeed_Inc=0.08</t>
   </si>
 </sst>
 </file>
@@ -720,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -729,7 +712,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -740,7 +723,7 @@
         <v>97</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>6</v>
@@ -879,7 +862,7 @@
         <v>16</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="E10" s="5">
         <v>5001</v>
@@ -893,10 +876,10 @@
         <v>98</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E11" s="5">
         <v>5002</v>
@@ -910,10 +893,10 @@
         <v>99</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="E12" s="5">
         <v>5003</v>
@@ -927,10 +910,10 @@
         <v>100</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E13" s="5">
         <v>5004</v>
@@ -944,10 +927,10 @@
         <v>97</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E14" s="6">
         <v>5005</v>
@@ -961,10 +944,10 @@
         <v>98</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E15" s="6">
         <v>5006</v>
@@ -978,10 +961,10 @@
         <v>99</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="E16" s="6">
         <v>5007</v>
@@ -995,10 +978,10 @@
         <v>100</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E17" s="6">
         <v>5008</v>
@@ -1012,10 +995,10 @@
         <v>97</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E18" s="3">
         <v>5001</v>
@@ -1029,10 +1012,10 @@
         <v>98</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E19" s="3">
         <v>5002</v>
@@ -1046,10 +1029,10 @@
         <v>99</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="E20" s="3">
         <v>5003</v>
@@ -1063,10 +1046,10 @@
         <v>100</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E21" s="3">
         <v>5004</v>
@@ -1080,10 +1063,10 @@
         <v>97</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E22" s="4">
         <v>5005</v>
@@ -1097,10 +1080,10 @@
         <v>98</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="E23" s="4">
         <v>5006</v>
@@ -1114,10 +1097,10 @@
         <v>99</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E24" s="4">
         <v>5007</v>
@@ -1131,10 +1114,10 @@
         <v>100</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="E25" s="4">
         <v>5008</v>
@@ -1148,10 +1131,10 @@
         <v>97</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E26" s="5">
         <v>5001</v>
@@ -1165,10 +1148,10 @@
         <v>98</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E27" s="5">
         <v>5002</v>
@@ -1182,10 +1165,10 @@
         <v>99</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E28" s="5">
         <v>5003</v>
@@ -1199,10 +1182,10 @@
         <v>100</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E29" s="8">
         <v>5004</v>
